--- a/approval_forms/039_policy_amendment_compliance_verification_form--approval_forms.xlsx
+++ b/approval_forms/039_policy_amendment_compliance_verification_form--approval_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="47" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>policy_amendment_compliance_verification_form</t>
+          <t>Form Title</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>organization</t>
+          <t>Organization</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>policy_version</t>
+          <t>Policy Version</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>effective_date</t>
+          <t>Effective Date</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>review_date</t>
+          <t>Review Date</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>Comments</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>approver</t>
+          <t>approver_1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>approver</t>
+          <t>Approver 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>approver</t>
+          <t>approver_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>approver</t>
+          <t>Approver 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>approver</t>
+          <t>approver_3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>approver</t>
+          <t>Approver 3</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>approver_2</t>
+          <t>approver_5</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>approver</t>
+          <t>Approver 5 - Yes/No</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>approver_3</t>
+          <t>approver_4</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>approver</t>
+          <t>Approver 4 - Approver1, Approver2, or Approver3</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>approver_4</t>
+          <t>approver_6</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>approver</t>
+          <t>Approver 6 - Yes/No</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,21 +791,136 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>approver_5</t>
+          <t>approver_7</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>approver</t>
+          <t>Approver 7 - Approver1 or Approver2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>select_multiple</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>approver_8</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Approver 8 - Approver1, Approver2, or Approver3</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>select_multiple</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>approver_9</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Approver 9 - Approver1 or Approver3</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>select_multiple</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>approver_10</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Approver 10 - Approver1 or Approver2</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>select_multiple</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>approver_11</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Approver 11 - Approver1 or Approver2 or Approver3</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>select_multiple</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>approver_12</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Approver 12 - Approver1 or Approver3</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -822,10 +937,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
@@ -850,7 +965,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>approver_choices</t>
+          <t>approver_1_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -867,7 +982,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>approver_choices</t>
+          <t>approver_1_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -884,7 +999,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>approver_choices</t>
+          <t>approver_1_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -901,7 +1016,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>approver_choices</t>
+          <t>approver_2_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -918,7 +1033,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>approver_choices</t>
+          <t>approver_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -935,7 +1050,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>approver_choices</t>
+          <t>approver_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,7 +1067,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>approver_choices</t>
+          <t>approver_3_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -969,7 +1084,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>approver_choices</t>
+          <t>approver_3_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -986,7 +1101,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>approver_choices</t>
+          <t>approver_3_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1003,68 +1118,68 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>approver_2_choices</t>
+          <t>approver_5_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>approver_2_choices</t>
+          <t>approver_5_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>approver_3_choices</t>
+          <t>approver_4_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>approver1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Approver1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>approver_3_choices</t>
+          <t>approver_4_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>approver2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Approver2</t>
         </is>
       </c>
     </row>
@@ -1076,63 +1191,267 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>approver3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Approver3</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>approver_4_choices</t>
+          <t>approver_6_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>approver_5_choices</t>
+          <t>approver_6_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>approver_5_choices</t>
+          <t>approver_7_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>approver1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Approver1</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>approver_7_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>approver2</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Approver2</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>approver_8_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>option_a</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Option A</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>approver_8_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>option_b</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Option B</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>approver_9_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>approver1</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Approver1</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>approver_9_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>approver3</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Approver3</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>approver_10_choices</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>approver1</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Approver1</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>approver_10_choices</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>approver2</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Approver2</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>approver_11_choices</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>approver1</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Approver1</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>approver_11_choices</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>approver2</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Approver2</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>approver_11_choices</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>approver3</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Approver3</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>approver_12_choices</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>approver1</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Approver1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>approver_12_choices</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>approver3</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Approver3</t>
         </is>
       </c>
     </row>
